--- a/pacjenci/MICHAŁ TRZÓSŁO.xlsx
+++ b/pacjenci/MICHAŁ TRZÓSŁO.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -542,17 +542,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4 - wychwyt umiarkowanie większy od wątroby</t>
+          <t>4 - utrzymujący się wychwyt patologiczny</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Częściowa odpowiedź metaboliczna na leczenie. Klasyfikacja Lugano: Partial Response (PR) - częściowa odpowiedź na leczenie. Deauville: 4 - wychwyt umiarkowanie większy od wątroby.</t>
+          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Brak aktywnej choroby</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -586,17 +586,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
+          <t>3 - wychwyt nie większy niż wątroba</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
+          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Brak aktywnej choroby</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -630,17 +630,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
+          <t>3 - wychwyt nie większy niż wątroba</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
+          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
         </is>
       </c>
     </row>

--- a/pacjenci/MICHAŁ TRZÓSŁO.xlsx
+++ b/pacjenci/MICHAŁ TRZÓSŁO.xlsx
@@ -413,235 +413,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>26.01.2023</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Choroba Hodgkina. Ocena zaawansowania.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  64min od podania 18F-FDG. Glikemia: 69mg%.</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Aktywne metabolicznie węzły chłonne przedziałów: IV obustronnie, V po stronie lewej, nadobojczykowe lewe wielkości do 23mm wg PET, SUV max do 6,6.  Aktywny metabolicznie obszar w grzbietowej części kości szczękowej po stronie prawej , z ubytkiem osteolitycznym - zmiana zapalna? naciekowa? - do kontroli stomatologicznej/laryngologicznej.  Asymetryczne pobudzenie metaboliczne w migdałku gardłowym prawym- do ew. kontroli laryngologicznej.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych Niewielkie prawowypukłe skrzywienie przegrody nosowej.  Zgrubienia zapalne błony śluzowej oraz przegroda kostna w prawej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne pojedyncze i spakietowane: - podobojczykowe lewe, śródpiersiowe wielkości do 39x22mm wg PET, SUV max do 11,8; - przytchawicze obustronnie, okna aortalno-płucnego wielkości do 42x24mm wg PET, SUV max do 9,5; - przy łuku aorty, przy tętnicy płucnej lewej wielkości do 41x32mm wg PET, SUV max do 10,6; - we wnękach obu płuc, podostrogowe, przyaortalne lewe, zamostkowe, nadprzeponowe lewe, wielkości do 41x27mm wg PET, SUV max do 10,9. Aktywne metabolicznie zmiany drobnoguzkowe w segm. 3 i 6 płuca lewego, wielkości do 11mm wg PET, SUV max do 3,4. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste przyśródpiersiowo w płacie górnym płuca lewego oraz nadprzeponowo.  Brzuch i miednica: Aktywny metabolicznie obszar podprzeponowo, lewobocznie od linii pośrodkowej, w przyleganiu do przyśrodkowego obrysu śledziony, wielkości 10mm wg PET, SUV max 4,3-drobny węzeł chłonny? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielka ilość płynu międzypętlowo w miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Wyraźne spłycenie fizjologicznych krzywizn kręgosłupa. Os sacrum arcuatum.  Wartości referencyjne: MBPS SUVmax do 1,8; Prawy płat wątroby SUVmax do 2,2.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego na szyi, w KLP oraz z pojedynczym obszarem [węzłem chłonnym?] w jamie brzusznej.  Aktywny metabolicznie obszar w grzbietowej części kości szczękowej po stronie prawej, z ubytkiem osteolitycznym - zmiana zapalna? naciekowa? - do kontroli stomatologicznej/laryngologicznej.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>11.8</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>08.05.2023</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Choroba Hodgkina. Wczesna ocena odpowiedzi.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 100mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Zwiększony metabolizm FDG w tkance brunatnej szyi z obecnością drobnych węzłów chłonnych w obrębie tkanki brunatnej, np. Im fuz. 53. Pobudzone metabolicznie węzły chłonne przedziału 2 i 3: po stronie lewej [Im 58] wielkości do 12mm, SUV max do 3,9 oraz po stronie prawej wielkości do 13mm, SUV max do 4,0. Asymetryczne pobudzenie metaboliczne w migdałku gardłowym prawym- do ew. kontroli laryngologicznej.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych Niewielkie prawowypukłe skrzywienie przegrody nosowej.  Drobne zgrubienia błony śluzowej oraz przegroda kostna w prawej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W śródpiersiu przednim pośrodkowo i po stronie lewej widoczny jest miernie hypodensyjny w przeglądowym badaniu TK obszar wielkości ok. 33x29mm - w pierwszej kolejności masa resztkowa z cechami rozpadu - dokładna ocena możliwa w badaniu TK KLP z kontrastem dożylnym. Niewielkie zmiany włókniste przyśródpiersiowo w płacie górnym płuca lewego oraz nadprzeponowo. drobny obszar miąższowo-włóknisty obwodowo w segm. 6 płuca prawego.  Brzuch i miednica: Niejednoznaczny obszar pobudzenia metabolicznego do przodu od pęcherza moczowego wielkości 12mm wg PET, SUV max 5,6 - uchyłek? inne?. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Wyraźne spłycenie fizjologicznych krzywizn kręgosłupa. Os sacrum arcuatum.  Inne: Zwiększony metabolizm FDG w tkance brunatnej szyi i KLP.  Wartości referencyjne: MBPS SUVmax do 2,2; Prawy płat wątroby SUVmax do 3,1.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność pobudzonych metabolicznie węzłów chłonnych przedziału 2 i 3 szyi, wśród zwiększonego metabolizmu tkanki tłuszczowej- do oceny z całością obrazu klinicznego. Regresja zmian w obrębie KLP - masa resztkowa w śródpiersiu do oceny w badaniu TK KLP z kontrastem dożylnym i do kontroli. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>5.6</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>04.07.2023</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Choroba Hodgkina. Ocena odpowiedzi po 4 cyklach cht przed ew. kwalifikacją do IFRT.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 59min od podania 18F-FDG. Glikemia: 92mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Asymetryczne pobudzenie metaboliczne w migdałku gardłowym prawym - do ew. kontroli laryngologicznej.  Zwiększony metabolizm FDG w topografii tkanki tłuszczowej brunatnej szyi i KLP- nie można jednoznacznie wykluczyć obecności drobnych węzłów chłonnych wśród pobudzonej tkanki tłuszczowej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych Niewielkie prawowypukłe skrzywienie przegrody nosowej.  Drobne zgrubienia błony śluzowej oraz przegroda kostna w prawej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W śródpiersiu przednim pośrodkowo i po stronie lewej widoczny jest miernie hypodensyjny w przeglądowym badaniu TK obszar wielkości ok. 39x28mm - w pierwszej kolejności masa resztkowa z cechami rozpadu - dokładna ocena możliwa w badaniu TK KLP z kontrastem dożylnym. Niewielkie zmiany włókniste przyśródpiersiowo w płacie górnym płuca lewego oraz nadprzeponowo. Drobny obszar miąższowo-włóknisty obwodowo w segm. 6 płuca prawego. Zwiększona ilość płynu w worku osierdziowym o szerokości płaszcza do 8mm, od strony PK serca. Poniżej serca otorbiony płyn, wielkości ok. 29x19mm.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Rozlanie wzmożony metabolizm FDG w układzie kostnym-związany ze stosowanym leczeniem? Wyraźne spłycenie fizjologicznych krzywizn kręgosłupa. Os sacrum arcuatum.   Wartości referencyjne: MBPS SUVmax do 1,7; Prawy płat wątroby SUVmax do 2,7.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech aktywnego metabolicznie procesu chłoniakowego w obszarze objętym badaniem. Masa resztkowa w śródpiersiu - do kontroli.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>2.7</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>01.02.2024</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Choroba Hodgkina. Ocena  remisji  choroby 3 m-ce po zakończeniu IFRT.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 57 min od podania 18F-FDG. Glikemia: 107 mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych Niewielkie prawowypukłe skrzywienie przegrody nosowej.  Drobne zgrubienia błony śluzowej oraz przegroda kostna w prawej zatoce szczękowej. ; Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W śródpiersiu przednim pośrodkowo i po stronie lewej widoczny jest miernie hypodensyjny w przeglądowym badaniu TK obszar wielkości ok. 26x15mm - w pierwszej kolejności masa resztkowa z cechami rozpadu - dokładna ocena możliwa w badaniu TK KLP z kontrastem dożylnym. Niewielkie zmiany włókniste przyśródpiersiowo w płacie górnym płuca lewego oraz nadprzeponowo. Niewielkie zmiany miąższowo-włókniste w segm. 1+2/3 przyśródpiersiowo. Drobny obszar miąższowo-włóknisty obwodowo w segm. 6 płuca prawego. W segm. 6 płuca lewego widoczny jest nieregularny obszar o typie mlecznej szyby z niewielkimi zmianami włóknistymi, wielkości 14x12mm. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym. Zwiększona ilość płynu w worku osierdziowym o szerokości płaszcza do 6mm, od strony PK i LK serca. Poniżej serca otorbiony płyn, wielkości ok. 29x21mm.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Drobne węzły chłonne przyaortalne i pachwinowe obustronnie.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Wyraźne spłycenie fizjologicznych krzywizn kręgosłupa. Niewielka dyskopatia na poziomie: L4/L5 i L5/S1. Os sacrum arcuatum.  Inne: Wzmożony metabolizm FDG w tkance brunatnej szyi i KLP-  nie można jednoznacznie wykluczyć obecności drobnych węzłów chłonnych wśród pobudzonej tkanki tłuszczowej.  Wartości referencyjne: MBPS SUVmax do 1,9; Prawy płat wątroby SUVmax do 3,4.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnego metabolicznie procesu chłoniakowego w obszarze objętym badaniem.  Masa resztkowa w śródpiersiu - do kontroli.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>3.4</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/MICHAŁ TRZÓSŁO.xlsx
+++ b/pacjenci/MICHAŁ TRZÓSŁO.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  64min od podania 18F-FDG. Glikemia: 69mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Aktywne metabolicznie węzły chłonne przedziałów: IV obustronnie, V po stronie lewej, nadobojczykowe lewe wielkości do 23mm wg PET, SUV max do 6,6.  Aktywny metabolicznie obszar w grzbietowej części kości szczękowej po stronie prawej , z ubytkiem osteolitycznym - zmiana zapalna? naciekowa? - do kontroli stomatologicznej/laryngologicznej.  Asymetryczne pobudzenie metaboliczne w migdałku gardłowym prawym- do ew. kontroli laryngologicznej.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych Niewielkie prawowypukłe skrzywienie przegrody nosowej.  Zgrubienia zapalne błony śluzowej oraz przegroda kostna w prawej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne pojedyncze i spakietowane: - podobojczykowe lewe, śródpiersiowe wielkości do 39x22mm wg PET, SUV max do 11,8; - przytchawicze obustronnie, okna aortalno-płucnego wielkości do 42x24mm wg PET, SUV max do 9,5; - przy łuku aorty, przy tętnicy płucnej lewej wielkości do 41x32mm wg PET, SUV max do 10,6; - we wnękach obu płuc, podostrogowe, przyaortalne lewe, zamostkowe, nadprzeponowe lewe, wielkości do 41x27mm wg PET, SUV max do 10,9. Aktywne metabolicznie zmiany drobnoguzkowe w segm. 3 i 6 płuca lewego, wielkości do 11mm wg PET, SUV max do 3,4. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste przyśródpiersiowo w płacie górnym płuca lewego oraz nadprzeponowo.  Brzuch i miednica: Aktywny metabolicznie obszar podprzeponowo, lewobocznie od linii pośrodkowej, w przyleganiu do przyśrodkowego obrysu śledziony, wielkości 10mm wg PET, SUV max 4,3-drobny węzeł chłonny? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielka ilość płynu międzypętlowo w miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Wyraźne spłycenie fizjologicznych krzywizn kręgosłupa. Os sacrum arcuatum.  Wartości referencyjne: MBPS SUVmax do 1,8; Prawy płat wątroby SUVmax do 2,2.</t>
+          <t>69</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne przedziałów: IV obustronnie, V po stronie lewej, nadobojczykowe lewe wielkości do 23mm wg PET, SUV max do 6,6.  Aktywny metabolicznie obszar w grzbietowej części kości szczękowej po stronie prawej , z ubytkiem osteolitycznym - zmiana zapalna? naciekowa? - do kontroli stomatologicznej/laryngologicznej.  Asymetryczne pobudzenie metaboliczne w migdałku gardłowym prawym- do ew. kontroli laryngologicznej.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych Niewielkie prawowypukłe skrzywienie przegrody nosowej.  Zgrubienia zapalne błony śluzowej oraz przegroda kostna w prawej zatoce szczękowej.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne pojedyncze i spakietowane: - podobojczykowe lewe, śródpiersiowe wielkości do 39x22mm wg PET, SUV max do 11,8; - przytchawicze obustronnie, okna aortalno-płucnego wielkości do 42x24mm wg PET, SUV max do 9,5; - przy łuku aorty, przy tętnicy płucnej lewej wielkości do 41x32mm wg PET, SUV max do 10,6; - we wnękach obu płuc, podostrogowe, przyaortalne lewe, zamostkowe, nadprzeponowe lewe, wielkości do 41x27mm wg PET, SUV max do 10,9. Aktywne metabolicznie zmiany drobnoguzkowe w segm. 3 i 6 płuca lewego, wielkości do 11mm wg PET, SUV max do 3,4. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste przyśródpiersiowo w płacie górnym płuca lewego oraz nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie obszar podprzeponowo, lewobocznie od linii pośrodkowej, w przyleganiu do przyśrodkowego obrysu śledziony, wielkości 10mm wg PET, SUV max 4,3-drobny węzeł chłonny? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielka ilość płynu międzypętlowo w miednicy.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Wyraźne spłycenie fizjologicznych krzywizn kręgosłupa. Os sacrum arcuatum.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego na szyi, w KLP oraz z pojedynczym obszarem [węzłem chłonnym?] w jamie brzusznej.  Aktywny metabolicznie obszar w grzbietowej części kości szczękowej po stronie prawej, z ubytkiem osteolitycznym - zmiana zapalna? naciekowa? - do kontroli stomatologicznej/laryngologicznej.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>11.8</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 100mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Zwiększony metabolizm FDG w tkance brunatnej szyi z obecnością drobnych węzłów chłonnych w obrębie tkanki brunatnej, np. Im fuz. 53. Pobudzone metabolicznie węzły chłonne przedziału 2 i 3: po stronie lewej [Im 58] wielkości do 12mm, SUV max do 3,9 oraz po stronie prawej wielkości do 13mm, SUV max do 4,0. Asymetryczne pobudzenie metaboliczne w migdałku gardłowym prawym- do ew. kontroli laryngologicznej.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych Niewielkie prawowypukłe skrzywienie przegrody nosowej.  Drobne zgrubienia błony śluzowej oraz przegroda kostna w prawej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W śródpiersiu przednim pośrodkowo i po stronie lewej widoczny jest miernie hypodensyjny w przeglądowym badaniu TK obszar wielkości ok. 33x29mm - w pierwszej kolejności masa resztkowa z cechami rozpadu - dokładna ocena możliwa w badaniu TK KLP z kontrastem dożylnym. Niewielkie zmiany włókniste przyśródpiersiowo w płacie górnym płuca lewego oraz nadprzeponowo. drobny obszar miąższowo-włóknisty obwodowo w segm. 6 płuca prawego.  Brzuch i miednica: Niejednoznaczny obszar pobudzenia metabolicznego do przodu od pęcherza moczowego wielkości 12mm wg PET, SUV max 5,6 - uchyłek? inne?. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Wyraźne spłycenie fizjologicznych krzywizn kręgosłupa. Os sacrum arcuatum.  Inne: Zwiększony metabolizm FDG w tkance brunatnej szyi i KLP.  Wartości referencyjne: MBPS SUVmax do 2,2; Prawy płat wątroby SUVmax do 3,1.</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Zwiększony metabolizm FDG w tkance brunatnej szyi z obecnością drobnych węzłów chłonnych w obrębie tkanki brunatnej, np. Im fuz. 53. Pobudzone metabolicznie węzły chłonne przedziału 2 i 3: po stronie lewej [Im 58] wielkości do 12mm, SUV max do 3,9 oraz po stronie prawej wielkości do 13mm, SUV max do 4,0. Asymetryczne pobudzenie metaboliczne w migdałku gardłowym prawym- do ew. kontroli laryngologicznej.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych Niewielkie prawowypukłe skrzywienie przegrody nosowej.  Drobne zgrubienia błony śluzowej oraz przegroda kostna w prawej zatoce szczękowej.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W śródpiersiu przednim pośrodkowo i po stronie lewej widoczny jest miernie hypodensyjny w przeglądowym badaniu TK obszar wielkości ok. 33x29mm - w pierwszej kolejności masa resztkowa z cechami rozpadu - dokładna ocena możliwa w badaniu TK KLP z kontrastem dożylnym. Niewielkie zmiany włókniste przyśródpiersiowo w płacie górnym płuca lewego oraz nadprzeponowo. drobny obszar miąższowo-włóknisty obwodowo w segm. 6 płuca prawego.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Niejednoznaczny obszar pobudzenia metabolicznego do przodu od pęcherza moczowego wielkości 12mm wg PET, SUV max 5,6 - uchyłek? inne?. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Wyraźne spłycenie fizjologicznych krzywizn kręgosłupa. Os sacrum arcuatum.  Inne: Zwiększony metabolizm FDG w tkance brunatnej szyi i KLP.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność pobudzonych metabolicznie węzłów chłonnych przedziału 2 i 3 szyi, wśród zwiększonego metabolizmu tkanki tłuszczowej- do oceny z całością obrazu klinicznego. Regresja zmian w obrębie KLP - masa resztkowa w śródpiersiu do oceny w badaniu TK KLP z kontrastem dożylnym i do kontroli. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>5.6</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 59min od podania 18F-FDG. Glikemia: 92mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Asymetryczne pobudzenie metaboliczne w migdałku gardłowym prawym - do ew. kontroli laryngologicznej.  Zwiększony metabolizm FDG w topografii tkanki tłuszczowej brunatnej szyi i KLP- nie można jednoznacznie wykluczyć obecności drobnych węzłów chłonnych wśród pobudzonej tkanki tłuszczowej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych Niewielkie prawowypukłe skrzywienie przegrody nosowej.  Drobne zgrubienia błony śluzowej oraz przegroda kostna w prawej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W śródpiersiu przednim pośrodkowo i po stronie lewej widoczny jest miernie hypodensyjny w przeglądowym badaniu TK obszar wielkości ok. 39x28mm - w pierwszej kolejności masa resztkowa z cechami rozpadu - dokładna ocena możliwa w badaniu TK KLP z kontrastem dożylnym. Niewielkie zmiany włókniste przyśródpiersiowo w płacie górnym płuca lewego oraz nadprzeponowo. Drobny obszar miąższowo-włóknisty obwodowo w segm. 6 płuca prawego. Zwiększona ilość płynu w worku osierdziowym o szerokości płaszcza do 8mm, od strony PK serca. Poniżej serca otorbiony płyn, wielkości ok. 29x19mm.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Rozlanie wzmożony metabolizm FDG w układzie kostnym-związany ze stosowanym leczeniem? Wyraźne spłycenie fizjologicznych krzywizn kręgosłupa. Os sacrum arcuatum.   Wartości referencyjne: MBPS SUVmax do 1,7; Prawy płat wątroby SUVmax do 2,7.</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Asymetryczne pobudzenie metaboliczne w migdałku gardłowym prawym - do ew. kontroli laryngologicznej.  Zwiększony metabolizm FDG w topografii tkanki tłuszczowej brunatnej szyi i KLP- nie można jednoznacznie wykluczyć obecności drobnych węzłów chłonnych wśród pobudzonej tkanki tłuszczowej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych Niewielkie prawowypukłe skrzywienie przegrody nosowej.  Drobne zgrubienia błony śluzowej oraz przegroda kostna w prawej zatoce szczękowej.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W śródpiersiu przednim pośrodkowo i po stronie lewej widoczny jest miernie hypodensyjny w przeglądowym badaniu TK obszar wielkości ok. 39x28mm - w pierwszej kolejności masa resztkowa z cechami rozpadu - dokładna ocena możliwa w badaniu TK KLP z kontrastem dożylnym. Niewielkie zmiany włókniste przyśródpiersiowo w płacie górnym płuca lewego oraz nadprzeponowo. Drobny obszar miąższowo-włóknisty obwodowo w segm. 6 płuca prawego. Zwiększona ilość płynu w worku osierdziowym o szerokości płaszcza do 8mm, od strony PK serca. Poniżej serca otorbiony płyn, wielkości ok. 29x19mm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Rozlanie wzmożony metabolizm FDG w układzie kostnym-związany ze stosowanym leczeniem? Wyraźne spłycenie fizjologicznych krzywizn kręgosłupa. Os sacrum arcuatum.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech aktywnego metabolicznie procesu chłoniakowego w obszarze objętym badaniem. Masa resztkowa w śródpiersiu - do kontroli.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>2.7</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 57 min od podania 18F-FDG. Glikemia: 107 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych Niewielkie prawowypukłe skrzywienie przegrody nosowej.  Drobne zgrubienia błony śluzowej oraz przegroda kostna w prawej zatoce szczękowej. ; Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W śródpiersiu przednim pośrodkowo i po stronie lewej widoczny jest miernie hypodensyjny w przeglądowym badaniu TK obszar wielkości ok. 26x15mm - w pierwszej kolejności masa resztkowa z cechami rozpadu - dokładna ocena możliwa w badaniu TK KLP z kontrastem dożylnym. Niewielkie zmiany włókniste przyśródpiersiowo w płacie górnym płuca lewego oraz nadprzeponowo. Niewielkie zmiany miąższowo-włókniste w segm. 1+2/3 przyśródpiersiowo. Drobny obszar miąższowo-włóknisty obwodowo w segm. 6 płuca prawego. W segm. 6 płuca lewego widoczny jest nieregularny obszar o typie mlecznej szyby z niewielkimi zmianami włóknistymi, wielkości 14x12mm. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym. Zwiększona ilość płynu w worku osierdziowym o szerokości płaszcza do 6mm, od strony PK i LK serca. Poniżej serca otorbiony płyn, wielkości ok. 29x21mm.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Drobne węzły chłonne przyaortalne i pachwinowe obustronnie.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Wyraźne spłycenie fizjologicznych krzywizn kręgosłupa. Niewielka dyskopatia na poziomie: L4/L5 i L5/S1. Os sacrum arcuatum.  Inne: Wzmożony metabolizm FDG w tkance brunatnej szyi i KLP-  nie można jednoznacznie wykluczyć obecności drobnych węzłów chłonnych wśród pobudzonej tkanki tłuszczowej.  Wartości referencyjne: MBPS SUVmax do 1,9; Prawy płat wątroby SUVmax do 3,4.</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych Niewielkie prawowypukłe skrzywienie przegrody nosowej.  Drobne zgrubienia błony śluzowej oraz przegroda kostna w prawej zatoce szczękowej. ;</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W śródpiersiu przednim pośrodkowo i po stronie lewej widoczny jest miernie hypodensyjny w przeglądowym badaniu TK obszar wielkości ok. 26x15mm - w pierwszej kolejności masa resztkowa z cechami rozpadu - dokładna ocena możliwa w badaniu TK KLP z kontrastem dożylnym. Niewielkie zmiany włókniste przyśródpiersiowo w płacie górnym płuca lewego oraz nadprzeponowo. Niewielkie zmiany miąższowo-włókniste w segm. 1+2/3 przyśródpiersiowo. Drobny obszar miąższowo-włóknisty obwodowo w segm. 6 płuca prawego. W segm. 6 płuca lewego widoczny jest nieregularny obszar o typie mlecznej szyby z niewielkimi zmianami włóknistymi, wielkości 14x12mm. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym. Zwiększona ilość płynu w worku osierdziowym o szerokości płaszcza do 6mm, od strony PK i LK serca. Poniżej serca otorbiony płyn, wielkości ok. 29x21mm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Drobne węzły chłonne przyaortalne i pachwinowe obustronnie.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Wyraźne spłycenie fizjologicznych krzywizn kręgosłupa. Niewielka dyskopatia na poziomie: L4/L5 i L5/S1. Os sacrum arcuatum.  Inne: Wzmożony metabolizm FDG w tkance brunatnej szyi i KLP-  nie można jednoznacznie wykluczyć obecności drobnych węzłów chłonnych wśród pobudzonej tkanki tłuszczowej.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnego metabolicznie procesu chłoniakowego w obszarze objętym badaniem.  Masa resztkowa w śródpiersiu - do kontroli.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>3.4</v>
       </c>
     </row>
